--- a/documentation/TripJournal-excel.xlsx
+++ b/documentation/TripJournal-excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\tripJournal-react\tripJournal-react\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484FF506-CE57-46EF-A471-1B7783FDDF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7F32E7-EF42-4740-927A-64727FD1D556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{C7EE0DD7-966E-4B7C-AB71-10C7A66B26EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{C7EE0DD7-966E-4B7C-AB71-10C7A66B26EA}"/>
   </bookViews>
   <sheets>
     <sheet name="planning" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="246">
   <si>
     <t>PLANNING</t>
   </si>
@@ -730,9 +730,6 @@
   </si>
   <si>
     <t>erd</t>
-  </si>
-  <si>
-    <t>in readme resources I think</t>
   </si>
   <si>
     <t>tiktok videos</t>
@@ -802,6 +799,12 @@
       </rPr>
       <t>in Gallery</t>
     </r>
+  </si>
+  <si>
+    <t>in readme resources</t>
+  </si>
+  <si>
+    <t>&lt;a href="https://www.maptiler.com/copyright/" target="_blank"&gt;&amp;copy; MapTiler&lt;/a&gt; &lt;a href="https://www.openstreetmap.org/copyright" target="_blank"&gt;&amp;copy; OpenStreetMap contributors&lt;/a&gt;</t>
   </si>
 </sst>
 </file>
@@ -1012,7 +1015,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1076,9 +1079,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1106,6 +1106,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1123,8 +1129,8 @@
   <colors>
     <mruColors>
       <color rgb="FFFFFFCC"/>
+      <color rgb="FFCCFFCC"/>
       <color rgb="FFFFCCCC"/>
-      <color rgb="FFCCFFCC"/>
       <color rgb="FF7A3F00"/>
       <color rgb="FF5A392B"/>
     </mruColors>
@@ -1466,12 +1472,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1767,11 +1773,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -2622,10 +2628,10 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="36" t="s">
         <v>165</v>
       </c>
       <c r="C2" s="30" t="s">
@@ -2636,7 +2642,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="35" t="s">
         <v>153</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -2650,7 +2656,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>154</v>
       </c>
       <c r="B4" s="14"/>
@@ -2678,7 +2684,7 @@
         <v>156</v>
       </c>
       <c r="B6" s="14"/>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="35" t="s">
         <v>171</v>
       </c>
       <c r="D6" s="29" t="s">
@@ -2691,9 +2697,9 @@
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="30" t="s">
-        <v>243</v>
-      </c>
-      <c r="D7" s="34" t="s">
+        <v>242</v>
+      </c>
+      <c r="D7" s="33" t="s">
         <v>177</v>
       </c>
     </row>
@@ -2701,7 +2707,7 @@
       <c r="A8" s="22"/>
       <c r="B8" s="18"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="34" t="s">
         <v>179</v>
       </c>
     </row>
@@ -2729,38 +2735,38 @@
       <c r="A11" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="33" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="35" t="s">
         <v>195</v>
       </c>
       <c r="C12" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="33" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="39" t="s">
         <v>182</v>
       </c>
       <c r="B13" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="35" t="s">
         <v>204</v>
       </c>
       <c r="D13" s="29" t="s">
@@ -2771,7 +2777,7 @@
       <c r="A14" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="42" t="s">
         <v>197</v>
       </c>
       <c r="C14" s="30" t="s">
@@ -2782,16 +2788,16 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="40" t="s">
         <v>184</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="42" t="s">
         <v>198</v>
       </c>
-      <c r="C15" s="43" t="s">
+      <c r="C15" s="42" t="s">
         <v>205</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="33" t="s">
         <v>213</v>
       </c>
     </row>
@@ -2802,24 +2808,24 @@
       <c r="B16" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="D16" s="33" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="42" t="s">
         <v>200</v>
       </c>
       <c r="C17" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="D17" s="33" t="s">
         <v>215</v>
       </c>
     </row>
@@ -2827,7 +2833,7 @@
       <c r="A18" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="35" t="s">
         <v>201</v>
       </c>
       <c r="C18" s="24"/>
@@ -2839,7 +2845,7 @@
       <c r="A19" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="42" t="s">
         <v>202</v>
       </c>
       <c r="C19" s="21"/>
@@ -2851,11 +2857,11 @@
       <c r="A20" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>244</v>
+      <c r="B20" s="37" t="s">
+        <v>243</v>
       </c>
       <c r="C20" s="21"/>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="33" t="s">
         <v>219</v>
       </c>
     </row>
@@ -2865,7 +2871,7 @@
       </c>
       <c r="B21" s="24"/>
       <c r="C21" s="21"/>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="33" t="s">
         <v>220</v>
       </c>
     </row>
@@ -2875,12 +2881,12 @@
       </c>
       <c r="B22" s="24"/>
       <c r="C22" s="21"/>
-      <c r="D22" s="34" t="s">
+      <c r="D22" s="33" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="38" t="s">
         <v>180</v>
       </c>
       <c r="B23" s="24"/>
@@ -2916,12 +2922,12 @@
       <c r="D27" s="14"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="42" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="43" t="s">
         <v>223</v>
       </c>
     </row>
@@ -2955,7 +2961,7 @@
         <v>75</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2965,11 +2971,11 @@
       <c r="B2" t="s">
         <v>227</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="F2" s="14" t="s">
+      <c r="D2" s="11" t="s">
         <v>231</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2977,65 +2983,63 @@
         <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" t="s">
         <v>237</v>
-      </c>
-      <c r="B4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B7" s="11" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="B9" s="36" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="B9" s="14" t="s">
+    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="B10" s="14"/>
+    </row>
+    <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="36" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="B10" s="14"/>
-    </row>
-    <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
-        <v>242</v>
-      </c>
       <c r="B11" s="14"/>
     </row>
-    <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>239</v>
-      </c>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="14"/>
       <c r="B12" s="14"/>
     </row>
   </sheetData>
@@ -3045,7 +3049,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBB21D28-5C13-49E6-A3F0-F30D14BDA424}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
@@ -3179,29 +3183,17 @@
         <v>13</v>
       </c>
     </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>245</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="4397f547-322f-44ba-b36f-2dbf78a6f97e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007358E0E606C72043B8DBF1C0A78D3264" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dc41e75d84cd78775c495471c7bc461a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="4397f547-322f-44ba-b36f-2dbf78a6f97e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361d89c18df4cd59fee7535e382182fc" ns3:_="">
     <xsd:import namespace="4397f547-322f-44ba-b36f-2dbf78a6f97e"/>
@@ -3395,10 +3387,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="4397f547-322f-44ba-b36f-2dbf78a6f97e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3478836B-5013-4DD3-BEB0-6FD4EF78AC96}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B422EBD-C3A7-4E61-95DE-293A94FD7B7D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4397f547-322f-44ba-b36f-2dbf78a6f97e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3420,19 +3439,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B422EBD-C3A7-4E61-95DE-293A94FD7B7D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3478836B-5013-4DD3-BEB0-6FD4EF78AC96}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4397f547-322f-44ba-b36f-2dbf78a6f97e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/documentation/TripJournal-excel.xlsx
+++ b/documentation/TripJournal-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\tripJournal-react\tripJournal-react\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7F32E7-EF42-4740-927A-64727FD1D556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42108D81-D321-40FD-B396-F6F9812E1DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{C7EE0DD7-966E-4B7C-AB71-10C7A66B26EA}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="256">
   <si>
     <t>PLANNING</t>
   </si>
@@ -805,6 +805,36 @@
   </si>
   <si>
     <t>&lt;a href="https://www.maptiler.com/copyright/" target="_blank"&gt;&amp;copy; MapTiler&lt;/a&gt; &lt;a href="https://www.openstreetmap.org/copyright" target="_blank"&gt;&amp;copy; OpenStreetMap contributors&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>use as guest</t>
+  </si>
+  <si>
+    <t>crud updated to db</t>
+  </si>
+  <si>
+    <t>gallery to db to specific user</t>
+  </si>
+  <si>
+    <t>publishing the app</t>
+  </si>
+  <si>
+    <t>app logo</t>
+  </si>
+  <si>
+    <t>ask users loging in with email for name</t>
+  </si>
+  <si>
+    <t>settings edit db update</t>
+  </si>
+  <si>
+    <t>stripe functionality</t>
+  </si>
+  <si>
+    <t>general to-do</t>
+  </si>
+  <si>
+    <t>globe fuckery</t>
   </si>
 </sst>
 </file>
@@ -1015,7 +1045,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1108,9 +1138,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2939,7 +2966,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA5DB0A2-9E41-4A79-A2B8-2B036B11F5C1}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -3001,13 +3028,19 @@
       <c r="B6" s="27" t="s">
         <v>239</v>
       </c>
+      <c r="D6" s="27" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="36" t="s">
         <v>238</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -3017,13 +3050,19 @@
       <c r="B8" s="36" t="s">
         <v>166</v>
       </c>
+      <c r="D8" s="4" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="36" t="s">
         <v>235</v>
       </c>
       <c r="B9" s="36" t="s">
         <v>240</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3031,16 +3070,52 @@
         <v>238</v>
       </c>
       <c r="B10" s="14"/>
+      <c r="D10" s="4" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
         <v>241</v>
       </c>
       <c r="B11" s="14"/>
+      <c r="D11" s="4" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
+      <c r="A12" s="36" t="s">
+        <v>246</v>
+      </c>
       <c r="B12" s="14"/>
+      <c r="D12" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D13" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D14" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D15" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D16" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D17" s="4" t="s">
+        <v>255</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/documentation/TripJournal-excel.xlsx
+++ b/documentation/TripJournal-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\tripJournal-react\tripJournal-react\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42108D81-D321-40FD-B396-F6F9812E1DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F095EA-5BE6-48EC-B58F-6A61DAB64A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{C7EE0DD7-966E-4B7C-AB71-10C7A66B26EA}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="258">
   <si>
     <t>PLANNING</t>
   </si>
@@ -745,9 +745,6 @@
   </si>
   <si>
     <t>login through google</t>
-  </si>
-  <si>
-    <t>login through facebook</t>
   </si>
   <si>
     <t>login with email + password</t>
@@ -835,6 +832,15 @@
   </si>
   <si>
     <t>globe fuckery</t>
+  </si>
+  <si>
+    <t>iteneraries- get gallery link authomatically from user input. Also suggest cities from an api (find one)</t>
+  </si>
+  <si>
+    <t>restrict access depending on a plan</t>
+  </si>
+  <si>
+    <t>login through microsoft</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1051,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1139,6 +1145,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1155,8 +1164,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCFFCC"/>
       <color rgb="FFFFFFCC"/>
-      <color rgb="FFCCFFCC"/>
       <color rgb="FFFFCCCC"/>
       <color rgb="FF7A3F00"/>
       <color rgb="FF5A392B"/>
@@ -2724,7 +2733,7 @@
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D7" s="33" t="s">
         <v>177</v>
@@ -2885,7 +2894,7 @@
         <v>188</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C20" s="21"/>
       <c r="D20" s="33" t="s">
@@ -2896,7 +2905,9 @@
       <c r="A21" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="B21" s="24"/>
+      <c r="B21" s="11" t="s">
+        <v>255</v>
+      </c>
       <c r="C21" s="21"/>
       <c r="D21" s="33" t="s">
         <v>220</v>
@@ -2998,7 +3009,7 @@
       <c r="B2" t="s">
         <v>227</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="4" t="s">
         <v>231</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -3010,15 +3021,15 @@
         <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B4" t="s">
         <v>236</v>
-      </c>
-      <c r="B4" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -3026,40 +3037,40 @@
         <v>232</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="B7" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>247</v>
+      <c r="B7" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="36" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="B8" s="36" t="s">
         <v>166</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
-        <v>235</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>240</v>
+      <c r="A9" s="45" t="s">
+        <v>234</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>239</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>233</v>
@@ -3067,54 +3078,57 @@
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B10" s="14"/>
       <c r="D10" s="4" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B11" s="14"/>
       <c r="D11" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="36" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B12" s="14"/>
-      <c r="D12" s="4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D12" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>256</v>
+      </c>
       <c r="D13" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D14" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D15" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D16" s="7" t="s">
         <v>252</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D16" s="4" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D17" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3260,7 +3274,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -3269,6 +3283,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="4397f547-322f-44ba-b36f-2dbf78a6f97e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007358E0E606C72043B8DBF1C0A78D3264" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dc41e75d84cd78775c495471c7bc461a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="4397f547-322f-44ba-b36f-2dbf78a6f97e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361d89c18df4cd59fee7535e382182fc" ns3:_="">
     <xsd:import namespace="4397f547-322f-44ba-b36f-2dbf78a6f97e"/>
@@ -3462,37 +3493,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="4397f547-322f-44ba-b36f-2dbf78a6f97e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B422EBD-C3A7-4E61-95DE-293A94FD7B7D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3478836B-5013-4DD3-BEB0-6FD4EF78AC96}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4397f547-322f-44ba-b36f-2dbf78a6f97e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3514,9 +3518,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3478836B-5013-4DD3-BEB0-6FD4EF78AC96}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B422EBD-C3A7-4E61-95DE-293A94FD7B7D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4397f547-322f-44ba-b36f-2dbf78a6f97e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>